--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="752">
   <si>
     <t>PII Service — API test cases by endpoint</t>
   </si>
   <si>
-    <t>Generated from the code with "npm run docs:testcases" on 2026-09-26. Last result from: local (no service) 2026-09-26 14:15 UTC. Click an endpoint to open its tab.</t>
+    <t>Generated from the code with "npm run docs:testcases" on 2026-09-26. Last result from: local (no service) 2026-09-26 14:37 UTC. Click an endpoint to open its tab.</t>
   </si>
   <si>
     <t>#</t>
@@ -150,7 +150,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Framework self-tests (no service needed): 81 — see the "Self-tests" tab.</t>
+    <t>Framework self-tests (no service needed): 82 — see the "Self-tests" tab.</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -381,7 +381,7 @@
     <t>Q-21</t>
   </si>
   <si>
-    <t>tests/security/authentication.spec.ts:257</t>
+    <t>tests/security/authentication.spec.ts:258</t>
   </si>
   <si>
     <t>PII-AZ-001</t>
@@ -441,7 +441,7 @@
     <t>Emails are saved without surrounding spaces and in lower case</t>
   </si>
   <si>
-    <t>tests/pii/normalization.spec.ts:37</t>
+    <t>tests/pii/normalization.spec.ts:36</t>
   </si>
   <si>
     <t>PII-NRM-002</t>
@@ -450,7 +450,7 @@
     <t>Phones are saved as digits only (spaces, dashes, brackets and + removed)</t>
   </si>
   <si>
-    <t>tests/pii/normalization.spec.ts:52</t>
+    <t>tests/pii/normalization.spec.ts:51</t>
   </si>
   <si>
     <t>PII-NRM-003</t>
@@ -459,7 +459,7 @@
     <t>Names are trimmed and repeated spaces collapsed; upper/lower case is kept</t>
   </si>
   <si>
-    <t>tests/pii/normalization.spec.ts:68</t>
+    <t>tests/pii/normalization.spec.ts:67</t>
   </si>
   <si>
     <t>PII-NRM-004</t>
@@ -468,7 +468,7 @@
     <t>Phones with exactly 8 and exactly 15 digits (the allowed limits) are accepted</t>
   </si>
   <si>
-    <t>tests/pii/normalization.spec.ts:84</t>
+    <t>tests/pii/normalization.spec.ts:83</t>
   </si>
   <si>
     <t>PII-NRM-005</t>
@@ -477,7 +477,7 @@
     <t>Values that are already clean are saved unchanged</t>
   </si>
   <si>
-    <t>tests/pii/normalization.spec.ts:114</t>
+    <t>tests/pii/normalization.spec.ts:113</t>
   </si>
   <si>
     <t>PII-SEC-001</t>
@@ -1722,7 +1722,7 @@
     <t>UT-CLI-002</t>
   </si>
   <si>
-    <t>Every request carries the four documented headers with correct values</t>
+    <t>Every request carries the documented headers (guide + tech doc) with correct values</t>
   </si>
   <si>
     <t>tests/unit/pii-client-wire.spec.ts:61</t>
@@ -1734,7 +1734,7 @@
     <t>Every request gets a new, unique request ID</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:72</t>
+    <t>tests/unit/pii-client-wire.spec.ts:77</t>
   </si>
   <si>
     <t>UT-CLI-004</t>
@@ -1743,7 +1743,7 @@
     <t>The search field name is safely encoded into the URL</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:79</t>
+    <t>tests/unit/pii-client-wire.spec.ts:84</t>
   </si>
   <si>
     <t>UT-CLI-005</t>
@@ -1752,7 +1752,7 @@
     <t>The health check is sent without security headers or a body</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:88</t>
+    <t>tests/unit/pii-client-wire.spec.ts:93</t>
   </si>
   <si>
     <t>UT-CLI-006</t>
@@ -1761,7 +1761,7 @@
     <t>Tests can remove headers, and no Content-Type is added behind their back</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:97</t>
+    <t>tests/unit/pii-client-wire.spec.ts:103</t>
   </si>
   <si>
     <t>UT-CLI-007</t>
@@ -1770,7 +1770,7 @@
     <t>Tests can deliberately send a body that differs from what was signed</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:108</t>
+    <t>tests/unit/pii-client-wire.spec.ts:115</t>
   </si>
   <si>
     <t>UT-CLI-008</t>
@@ -1779,7 +1779,7 @@
     <t>Tests can sign with another key or the wrong method while keeping the caller ID</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:120</t>
+    <t>tests/unit/pii-client-wire.spec.ts:127</t>
   </si>
   <si>
     <t>UT-CLI-009</t>
@@ -1788,7 +1788,7 @@
     <t>Read-only calls retry on 503 with a new request ID, a limited number of times</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:134</t>
+    <t>tests/unit/pii-client-wire.spec.ts:141</t>
   </si>
   <si>
     <t>UT-CLI-010</t>
@@ -1797,7 +1797,7 @@
     <t>Saves are never retried, and 401/403 responses are never retried</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:151</t>
+    <t>tests/unit/pii-client-wire.spec.ts:158</t>
   </si>
   <si>
     <t>UT-CLI-011</t>
@@ -1806,7 +1806,7 @@
     <t>Non-JSON and empty responses are handled, and response bodies are never printed</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:172</t>
+    <t>tests/unit/pii-client-wire.spec.ts:179</t>
   </si>
   <si>
     <t>UT-CLI-012</t>
@@ -1815,7 +1815,7 @@
     <t>Logs contain request details but no personal data, signatures or bodies</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:194</t>
+    <t>tests/unit/pii-client-wire.spec.ts:201</t>
   </si>
   <si>
     <t>UT-CLI-013</t>
@@ -1824,7 +1824,7 @@
     <t>Calling a signed endpoint with no caller set up fails early with a clear message</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:205</t>
+    <t>tests/unit/pii-client-wire.spec.ts:212</t>
   </si>
   <si>
     <t>UT-CLI-014</t>
@@ -1833,7 +1833,7 @@
     <t>Network errors are reported without the request body or headers</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:216</t>
+    <t>tests/unit/pii-client-wire.spec.ts:223</t>
   </si>
   <si>
     <t>UT-CLI-015</t>
@@ -1842,7 +1842,7 @@
     <t>Every logged call is labelled as test, setup or verification</t>
   </si>
   <si>
-    <t>tests/unit/pii-client-wire.spec.ts:225</t>
+    <t>tests/unit/pii-client-wire.spec.ts:232</t>
   </si>
   <si>
     <t>Clean-up</t>
@@ -2122,6 +2122,15 @@
   </si>
   <si>
     <t>tests/unit/redaction-logger.spec.ts:91</t>
+  </si>
+  <si>
+    <t>UT-RED-008</t>
+  </si>
+  <si>
+    <t>The body-hash header (an unkeyed hash of PII) is never logged, by key or as free text</t>
+  </si>
+  <si>
+    <t>tests/unit/redaction-logger.spec.ts:115</t>
   </si>
   <si>
     <t>Retries</t>
@@ -4293,7 +4302,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4704,8 +4713,8 @@
       <c r="C24" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>9</v>
+      <c r="D24" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>566</v>
@@ -5427,24 +5436,24 @@
     </row>
     <row r="67" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>699</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="C67" s="17" t="s">
         <v>700</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="D67" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>701</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="68" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>703</v>
@@ -5461,24 +5470,24 @@
     </row>
     <row r="69" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="B69" s="16" t="s">
         <v>706</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="C69" s="17" t="s">
         <v>707</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>708</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>9</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>710</v>
@@ -5495,7 +5504,7 @@
     </row>
     <row r="71" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>713</v>
@@ -5512,7 +5521,7 @@
     </row>
     <row r="72" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>716</v>
@@ -5529,7 +5538,7 @@
     </row>
     <row r="73" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B73" s="16" t="s">
         <v>719</v>
@@ -5546,7 +5555,7 @@
     </row>
     <row r="74" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>722</v>
@@ -5563,7 +5572,7 @@
     </row>
     <row r="75" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B75" s="16" t="s">
         <v>725</v>
@@ -5580,7 +5589,7 @@
     </row>
     <row r="76" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>728</v>
@@ -5597,7 +5606,7 @@
     </row>
     <row r="77" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B77" s="16" t="s">
         <v>731</v>
@@ -5614,7 +5623,7 @@
     </row>
     <row r="78" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>734</v>
@@ -5631,7 +5640,7 @@
     </row>
     <row r="79" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B79" s="16" t="s">
         <v>737</v>
@@ -5648,7 +5657,7 @@
     </row>
     <row r="80" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>740</v>
@@ -5665,7 +5674,7 @@
     </row>
     <row r="81" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B81" s="16" t="s">
         <v>743</v>
@@ -5682,7 +5691,7 @@
     </row>
     <row r="82" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>746</v>
@@ -5695,6 +5704,23 @@
       </c>
       <c r="E82" s="15" t="s">
         <v>748</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>709</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>751</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="729">
   <si>
     <t>PII Service — API Test Cases</t>
   </si>
   <si>
-    <t>Last run: 2026-09-27 05:03 UTC  ·  environment local (no service)  ·  projects=unit  ·  took 3.6s</t>
+    <t>Last run: 2026-09-28 08:45 UTC  ·  environment local (no service)  ·  projects=unit  ·  took 4.3s</t>
   </si>
   <si>
     <t>Total test cases: 133</t>
@@ -67,121 +67,46 @@
     <t>Go to</t>
   </si>
   <si>
-    <t>Health check</t>
-  </si>
-  <si>
     <t>GET /health/ready</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Go to section 1 →</t>
-  </si>
-  <si>
-    <t>Save PII</t>
-  </si>
-  <si>
     <t>POST /api/v1/pii</t>
   </si>
   <si>
-    <t>Go to section 2 →</t>
-  </si>
-  <si>
-    <t>Read PII</t>
-  </si>
-  <si>
     <t>POST /api/v1/pii/read</t>
   </si>
   <si>
-    <t>Go to section 3 →</t>
-  </si>
-  <si>
-    <t>Search PII</t>
-  </si>
-  <si>
     <t>POST /api/v1/pii/{field}/search</t>
   </si>
   <si>
-    <t>Go to section 4 →</t>
-  </si>
-  <si>
-    <t>Bulk read PII</t>
-  </si>
-  <si>
     <t>POST /api/v1/pii/batch/read</t>
   </si>
   <si>
-    <t>Go to section 5 →</t>
-  </si>
-  <si>
-    <t>Create temporary phone</t>
-  </si>
-  <si>
     <t>POST /api/v1/transient/phones</t>
   </si>
   <si>
-    <t>Go to section 6 →</t>
-  </si>
-  <si>
-    <t>Look up temporary phone</t>
-  </si>
-  <si>
     <t>POST /api/v1/transient/phones/resolve</t>
   </si>
   <si>
-    <t>Go to section 7 →</t>
-  </si>
-  <si>
-    <t>Promote temporary phone</t>
-  </si>
-  <si>
     <t>POST /api/v1/transient/phones/promote</t>
   </si>
   <si>
-    <t>Go to section 8 →</t>
-  </si>
-  <si>
-    <t>Create encryption key</t>
-  </si>
-  <si>
     <t>POST /api/v1/free-text/keys</t>
   </si>
   <si>
-    <t>Go to section 9 →</t>
-  </si>
-  <si>
-    <t>Read encryption key</t>
-  </si>
-  <si>
     <t>POST /api/v1/free-text/keys/read</t>
   </si>
   <si>
-    <t>Go to section 10 →</t>
-  </si>
-  <si>
-    <t>Revoke encryption key</t>
-  </si>
-  <si>
     <t>POST /api/v1/free-text/keys/revoke</t>
   </si>
   <si>
-    <t>Go to section 11 →</t>
-  </si>
-  <si>
-    <t>Across endpoints</t>
-  </si>
-  <si>
     <t>several endpoints</t>
   </si>
   <si>
-    <t>Go to section 12 →</t>
-  </si>
-  <si>
     <t>1.  Health check     GET /health/ready        2 test cases  ·  ✔ 0  ·  ✘ 0  ·  — 2</t>
-  </si>
-  <si>
-    <t>↑ Summary</t>
   </si>
   <si>
     <t>What this endpoint does: Readiness check.</t>
@@ -5139,12 +5064,13 @@
       <c r="A7" s="9">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>17</v>
+      <c r="B7" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A21","Health check")</f>
+        <v>Health check</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="9">
@@ -5160,10 +5086,11 @@
         <v>2</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="K7" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A21","Go to section 1 →")</f>
+        <v>Go to section 1 →</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
@@ -5172,12 +5099,13 @@
       <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>21</v>
+      <c r="B8" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A27","Save PII")</f>
+        <v>Save PII</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="16">
@@ -5193,10 +5121,11 @@
         <v>55</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="K8" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A27","Go to section 2 →")</f>
+        <v>Go to section 2 →</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="22"/>
@@ -5205,12 +5134,13 @@
       <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>24</v>
+      <c r="B9" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A86","Read PII")</f>
+        <v>Read PII</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="9">
@@ -5226,10 +5156,11 @@
         <v>15</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="K9" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A86","Go to section 3 →")</f>
+        <v>Go to section 3 →</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -5238,12 +5169,13 @@
       <c r="A10" s="16">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>27</v>
+      <c r="B10" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A105","Search PII")</f>
+        <v>Search PII</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="16">
@@ -5259,10 +5191,11 @@
         <v>16</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="K10" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A105","Go to section 4 →")</f>
+        <v>Go to section 4 →</v>
       </c>
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
@@ -5271,12 +5204,13 @@
       <c r="A11" s="9">
         <v>5</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>30</v>
+      <c r="B11" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A125","Bulk read PII")</f>
+        <v>Bulk read PII</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="9">
@@ -5292,10 +5226,11 @@
         <v>10</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="K11" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A125","Go to section 5 →")</f>
+        <v>Go to section 5 →</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
@@ -5304,12 +5239,13 @@
       <c r="A12" s="16">
         <v>6</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>33</v>
+      <c r="B12" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A139","Create temporary phone")</f>
+        <v>Create temporary phone</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="18" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="16">
@@ -5325,10 +5261,11 @@
         <v>7</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="K12" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A139","Go to section 6 →")</f>
+        <v>Go to section 6 →</v>
       </c>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
@@ -5337,12 +5274,13 @@
       <c r="A13" s="9">
         <v>7</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>36</v>
+      <c r="B13" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A150","Look up temporary phone")</f>
+        <v>Look up temporary phone</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="11" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="9">
@@ -5358,10 +5296,11 @@
         <v>6</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="K13" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A150","Go to section 7 →")</f>
+        <v>Go to section 7 →</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
@@ -5370,12 +5309,13 @@
       <c r="A14" s="16">
         <v>8</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>39</v>
+      <c r="B14" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A160","Promote temporary phone")</f>
+        <v>Promote temporary phone</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="18" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="16">
@@ -5391,10 +5331,11 @@
         <v>2</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>41</v>
+        <v>18</v>
+      </c>
+      <c r="K14" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A160","Go to section 8 →")</f>
+        <v>Go to section 8 →</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
@@ -5403,12 +5344,13 @@
       <c r="A15" s="9">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>42</v>
+      <c r="B15" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A166","Create encryption key")</f>
+        <v>Create encryption key</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="11" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="9">
@@ -5424,10 +5366,11 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="K15" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A166","Go to section 9 →")</f>
+        <v>Go to section 9 →</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -5436,12 +5379,13 @@
       <c r="A16" s="16">
         <v>10</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>45</v>
+      <c r="B16" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A175","Read encryption key")</f>
+        <v>Read encryption key</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="18" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="16">
@@ -5457,10 +5401,11 @@
         <v>4</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>47</v>
+        <v>18</v>
+      </c>
+      <c r="K16" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A175","Go to section 10 →")</f>
+        <v>Go to section 10 →</v>
       </c>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
@@ -5469,12 +5414,13 @@
       <c r="A17" s="9">
         <v>11</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>48</v>
+      <c r="B17" s="10" t="str">
+        <f>HYPERLINK("#'Test Cases'!A183","Revoke encryption key")</f>
+        <v>Revoke encryption key</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="11" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="9">
@@ -5490,10 +5436,11 @@
         <v>2</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="K17" s="15" t="str">
+        <f>HYPERLINK("#'Test Cases'!A183","Go to section 11 →")</f>
+        <v>Go to section 11 →</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
@@ -5502,12 +5449,13 @@
       <c r="A18" s="16">
         <v>12</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>51</v>
+      <c r="B18" s="17" t="str">
+        <f>HYPERLINK("#'Test Cases'!A189","Across endpoints")</f>
+        <v>Across endpoints</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="16">
@@ -5523,17 +5471,18 @@
         <v>9</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="K18" s="22" t="str">
+        <f>HYPERLINK("#'Test Cases'!A189","Go to section 12 →")</f>
+        <v>Go to section 12 →</v>
       </c>
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -5546,13 +5495,14 @@
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="24" t="s">
-        <v>55</v>
+      <c r="M21" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -5569,43 +5519,43 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K23" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M23" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5613,40 +5563,40 @@
         <v>1</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J24" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L24" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M24" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5654,45 +5604,45 @@
         <v>2</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I25" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L25" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
@@ -5705,13 +5655,14 @@
       <c r="J27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
-      <c r="M27" s="24" t="s">
-        <v>55</v>
+      <c r="M27" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
@@ -5728,43 +5679,43 @@
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K29" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L29" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5772,40 +5723,40 @@
         <v>1</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I30" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J30" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M30" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5813,40 +5764,40 @@
         <v>2</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H31" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L31" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5854,40 +5805,40 @@
         <v>3</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J32" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M32" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5895,40 +5846,40 @@
         <v>4</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L33" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5936,40 +5887,40 @@
         <v>5</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H34" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J34" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L34" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5977,40 +5928,40 @@
         <v>6</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L35" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M35" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6018,40 +5969,40 @@
         <v>7</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G36" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I36" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6059,40 +6010,40 @@
         <v>8</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H37" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L37" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M37" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6100,40 +6051,40 @@
         <v>9</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G38" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L38" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M38" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6141,40 +6092,40 @@
         <v>10</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G39" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L39" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M39" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6182,40 +6133,40 @@
         <v>11</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G40" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H40" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I40" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J40" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6223,40 +6174,40 @@
         <v>12</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G41" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H41" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I41" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K41" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L41" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M41" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6264,40 +6215,40 @@
         <v>13</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G42" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H42" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I42" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J42" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K42" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M42" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6305,40 +6256,40 @@
         <v>14</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I43" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L43" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M43" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6346,40 +6297,40 @@
         <v>15</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G44" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H44" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I44" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J44" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K44" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M44" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6387,40 +6338,40 @@
         <v>16</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G45" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H45" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I45" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L45" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M45" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6428,40 +6379,40 @@
         <v>17</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G46" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H46" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I46" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="K46" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L46" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6469,40 +6420,40 @@
         <v>18</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E47" s="37" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="G47" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H47" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I47" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J47" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L47" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M47" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6510,40 +6461,40 @@
         <v>19</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="G48" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H48" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I48" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J48" s="29" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L48" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M48" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6551,40 +6502,40 @@
         <v>20</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="G49" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H49" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L49" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M49" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6592,40 +6543,40 @@
         <v>21</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="G50" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J50" s="29" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="K50" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6633,40 +6584,40 @@
         <v>22</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E51" s="37" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="G51" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H51" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K51" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L51" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M51" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6674,40 +6625,40 @@
         <v>23</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="G52" s="27" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H52" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I52" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J52" s="29" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M52" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6715,40 +6666,40 @@
         <v>24</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="G53" s="35" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H53" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L53" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M53" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6756,40 +6707,40 @@
         <v>25</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="G54" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H54" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M54" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" ht="111" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6797,40 +6748,40 @@
         <v>26</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="E55" s="37" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H55" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L55" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M55" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6838,40 +6789,40 @@
         <v>27</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="G56" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I56" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J56" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K56" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M56" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6879,40 +6830,40 @@
         <v>28</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="G57" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H57" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I57" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L57" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M57" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6920,40 +6871,40 @@
         <v>29</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="E58" s="29" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="G58" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J58" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M58" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -6961,40 +6912,40 @@
         <v>30</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="G59" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H59" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I59" s="47" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L59" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M59" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7002,40 +6953,40 @@
         <v>31</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="G60" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H60" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J60" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L60" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M60" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7043,40 +6994,40 @@
         <v>32</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="G61" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H61" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I61" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L61" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M61" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7084,40 +7035,40 @@
         <v>33</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="C62" s="29" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="G62" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H62" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I62" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J62" s="29" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="K62" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L62" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M62" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7125,40 +7076,40 @@
         <v>34</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="C63" s="37" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="G63" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H63" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I63" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J63" s="37" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K63" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L63" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M63" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7166,40 +7117,40 @@
         <v>35</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="G64" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H64" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I64" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J64" s="29" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K64" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L64" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M64" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7207,40 +7158,40 @@
         <v>36</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="G65" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H65" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I65" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L65" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M65" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7248,40 +7199,40 @@
         <v>37</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="G66" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H66" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I66" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J66" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K66" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L66" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7289,40 +7240,40 @@
         <v>38</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="G67" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J67" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L67" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M67" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7330,40 +7281,40 @@
         <v>39</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="G68" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H68" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I68" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J68" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K68" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L68" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M68" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7371,40 +7322,40 @@
         <v>40</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="G69" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I69" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J69" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K69" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L69" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M69" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7412,40 +7363,40 @@
         <v>41</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E70" s="29" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="G70" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H70" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I70" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J70" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K70" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L70" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M70" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7453,40 +7404,40 @@
         <v>42</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="G71" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I71" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K71" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L71" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M71" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7494,40 +7445,40 @@
         <v>43</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="G72" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H72" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I72" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J72" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K72" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L72" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M72" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7535,40 +7486,40 @@
         <v>44</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="G73" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H73" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I73" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J73" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L73" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M73" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7576,40 +7527,40 @@
         <v>45</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="E74" s="29" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="G74" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H74" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I74" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J74" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K74" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L74" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M74" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7617,40 +7568,40 @@
         <v>46</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="G75" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H75" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I75" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J75" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K75" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L75" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M75" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7658,40 +7609,40 @@
         <v>47</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="E76" s="29" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="G76" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H76" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I76" s="49" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J76" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K76" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L76" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M76" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7699,40 +7650,40 @@
         <v>48</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="G77" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I77" s="47" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J77" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K77" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L77" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M77" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7740,40 +7691,40 @@
         <v>49</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="E78" s="29" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="G78" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H78" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I78" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J78" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K78" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L78" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M78" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7781,40 +7732,40 @@
         <v>50</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="C79" s="37" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="G79" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I79" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J79" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K79" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L79" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M79" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7822,40 +7773,40 @@
         <v>51</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C80" s="29" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="G80" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H80" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I80" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J80" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K80" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L80" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M80" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7863,40 +7814,40 @@
         <v>52</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="G81" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H81" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I81" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J81" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K81" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L81" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M81" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7904,40 +7855,40 @@
         <v>53</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="C82" s="29" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="E82" s="29" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="F82" s="29" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="G82" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H82" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I82" s="49" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J82" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K82" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L82" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M82" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7945,40 +7896,40 @@
         <v>54</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="G83" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H83" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I83" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J83" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K83" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L83" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M83" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" ht="156" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7986,45 +7937,45 @@
         <v>55</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="E84" s="29" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="G84" s="27" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I84" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J84" s="29" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="K84" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L84" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M84" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="23" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="B86" s="23"/>
       <c r="C86" s="23"/>
@@ -8037,13 +7988,14 @@
       <c r="J86" s="23"/>
       <c r="K86" s="23"/>
       <c r="L86" s="23"/>
-      <c r="M86" s="24" t="s">
-        <v>55</v>
+      <c r="M86" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -8060,43 +8012,43 @@
     </row>
     <row r="88" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G88" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I88" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K88" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L88" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M88" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8104,40 +8056,40 @@
         <v>1</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="E89" s="29" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="G89" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H89" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I89" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J89" s="29" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K89" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L89" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M89" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8145,40 +8097,40 @@
         <v>2</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="E90" s="37" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="G90" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H90" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I90" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J90" s="37" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K90" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L90" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M90" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8186,40 +8138,40 @@
         <v>3</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="E91" s="29" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="G91" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H91" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I91" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J91" s="29" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K91" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L91" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M91" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8227,40 +8179,40 @@
         <v>4</v>
       </c>
       <c r="B92" s="36" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="C92" s="37" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="E92" s="37" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="G92" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H92" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I92" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J92" s="37" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K92" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L92" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M92" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8268,40 +8220,40 @@
         <v>5</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="E93" s="29" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="F93" s="29" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="G93" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H93" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I93" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J93" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K93" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L93" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M93" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8309,40 +8261,40 @@
         <v>6</v>
       </c>
       <c r="B94" s="36" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="E94" s="37" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="G94" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H94" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I94" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J94" s="37" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K94" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L94" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M94" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8350,40 +8302,40 @@
         <v>7</v>
       </c>
       <c r="B95" s="28" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="E95" s="29" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="F95" s="29" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="G95" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H95" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I95" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J95" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K95" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L95" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M95" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8391,40 +8343,40 @@
         <v>8</v>
       </c>
       <c r="B96" s="36" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C96" s="37" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="E96" s="37" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="G96" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H96" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I96" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J96" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K96" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L96" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M96" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8432,40 +8384,40 @@
         <v>9</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="E97" s="29" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G97" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H97" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I97" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K97" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L97" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M97" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8473,40 +8425,40 @@
         <v>10</v>
       </c>
       <c r="B98" s="36" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="E98" s="37" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G98" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H98" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I98" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J98" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K98" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L98" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M98" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8514,40 +8466,40 @@
         <v>11</v>
       </c>
       <c r="B99" s="28" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C99" s="29" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E99" s="29" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="G99" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H99" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I99" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J99" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K99" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L99" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M99" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8555,40 +8507,40 @@
         <v>12</v>
       </c>
       <c r="B100" s="36" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="E100" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="G100" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H100" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I100" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J100" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K100" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L100" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M100" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8596,40 +8548,40 @@
         <v>13</v>
       </c>
       <c r="B101" s="28" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="C101" s="29" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="D101" s="30" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="E101" s="29" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="G101" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H101" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I101" s="49" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K101" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L101" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M101" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8637,40 +8589,40 @@
         <v>14</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="E102" s="37" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="G102" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H102" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I102" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J102" s="37" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K102" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L102" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8678,45 +8630,45 @@
         <v>15</v>
       </c>
       <c r="B103" s="28" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="C103" s="29" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="E103" s="29" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="G103" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H103" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I103" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J103" s="29" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="K103" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L103" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M103" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="B105" s="23"/>
       <c r="C105" s="23"/>
@@ -8729,13 +8681,14 @@
       <c r="J105" s="23"/>
       <c r="K105" s="23"/>
       <c r="L105" s="23"/>
-      <c r="M105" s="24" t="s">
-        <v>55</v>
+      <c r="M105" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="25" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="B106" s="25"/>
       <c r="C106" s="25"/>
@@ -8752,43 +8705,43 @@
     </row>
     <row r="107" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H107" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I107" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J107" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K107" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L107" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M107" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8796,40 +8749,40 @@
         <v>1</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C108" s="29" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="E108" s="29" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="G108" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H108" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I108" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J108" s="29" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K108" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L108" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8837,40 +8790,40 @@
         <v>2</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="E109" s="37" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="F109" s="37" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="G109" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H109" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I109" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J109" s="37" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K109" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L109" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M109" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8878,40 +8831,40 @@
         <v>3</v>
       </c>
       <c r="B110" s="28" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="C110" s="29" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="E110" s="29" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="F110" s="29" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="G110" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H110" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I110" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J110" s="29" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="K110" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L110" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M110" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8919,40 +8872,40 @@
         <v>4</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="D111" s="38" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="E111" s="37" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="F111" s="37" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="G111" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H111" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I111" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J111" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K111" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L111" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M111" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8960,40 +8913,40 @@
         <v>5</v>
       </c>
       <c r="B112" s="28" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="C112" s="29" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="E112" s="29" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="F112" s="29" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="G112" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H112" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I112" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J112" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K112" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L112" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M112" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9001,40 +8954,40 @@
         <v>6</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="C113" s="37" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="D113" s="38" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="E113" s="37" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="F113" s="37" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="G113" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H113" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I113" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J113" s="37" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K113" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L113" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M113" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9042,40 +8995,40 @@
         <v>7</v>
       </c>
       <c r="B114" s="28" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="C114" s="29" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="E114" s="29" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="F114" s="29" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="G114" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H114" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J114" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K114" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L114" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M114" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9083,40 +9036,40 @@
         <v>8</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="D115" s="38" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="E115" s="37" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="G115" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H115" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I115" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J115" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K115" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L115" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M115" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9124,40 +9077,40 @@
         <v>9</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="C116" s="29" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="E116" s="29" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="F116" s="29" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="G116" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H116" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I116" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J116" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K116" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L116" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M116" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9165,40 +9118,40 @@
         <v>10</v>
       </c>
       <c r="B117" s="36" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="D117" s="38" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="E117" s="37" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="G117" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H117" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I117" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J117" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K117" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L117" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M117" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9206,40 +9159,40 @@
         <v>11</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="D118" s="30" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="E118" s="29" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="G118" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H118" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I118" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J118" s="29" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="K118" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L118" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M118" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9247,40 +9200,40 @@
         <v>12</v>
       </c>
       <c r="B119" s="36" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="D119" s="38" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="E119" s="37" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="G119" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H119" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I119" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J119" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K119" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L119" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M119" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9288,40 +9241,40 @@
         <v>13</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
       <c r="E120" s="29" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="G120" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H120" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I120" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J120" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K120" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L120" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M120" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9329,40 +9282,40 @@
         <v>14</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="D121" s="38" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="E121" s="37" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="G121" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H121" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I121" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J121" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K121" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L121" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M121" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="122" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9370,40 +9323,40 @@
         <v>15</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="C122" s="29" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="D122" s="30" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="E122" s="29" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="F122" s="29" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="G122" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H122" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I122" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J122" s="29" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="K122" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L122" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9411,45 +9364,45 @@
         <v>16</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="D123" s="38" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="E123" s="37" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="F123" s="37" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="G123" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H123" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I123" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J123" s="37" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K123" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L123" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M123" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="23" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="B125" s="23"/>
       <c r="C125" s="23"/>
@@ -9462,13 +9415,14 @@
       <c r="J125" s="23"/>
       <c r="K125" s="23"/>
       <c r="L125" s="23"/>
-      <c r="M125" s="24" t="s">
-        <v>55</v>
+      <c r="M125" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="25" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="B126" s="25"/>
       <c r="C126" s="25"/>
@@ -9485,43 +9439,43 @@
     </row>
     <row r="127" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B127" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E127" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G127" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H127" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I127" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J127" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K127" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L127" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M127" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9529,40 +9483,40 @@
         <v>1</v>
       </c>
       <c r="B128" s="28" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="C128" s="29" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D128" s="30" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="E128" s="29" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="F128" s="29" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="G128" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H128" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I128" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J128" s="29" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K128" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L128" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M128" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="129" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9570,40 +9524,40 @@
         <v>2</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="D129" s="38" t="s">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="E129" s="37" t="s">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="F129" s="37" t="s">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="G129" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H129" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I129" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J129" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K129" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L129" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M129" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9611,40 +9565,40 @@
         <v>3</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="C130" s="29" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="D130" s="30" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="E130" s="29" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="F130" s="29" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="G130" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H130" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I130" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J130" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K130" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L130" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M130" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="131" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9652,40 +9606,40 @@
         <v>4</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="C131" s="37" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D131" s="38" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="E131" s="37" t="s">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="F131" s="37" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G131" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H131" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I131" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J131" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K131" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L131" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M131" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9693,40 +9647,40 @@
         <v>5</v>
       </c>
       <c r="B132" s="28" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="C132" s="29" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="D132" s="30" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="E132" s="29" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="F132" s="29" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="G132" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H132" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I132" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J132" s="29" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="K132" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L132" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M132" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="133" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9734,40 +9688,40 @@
         <v>6</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="C133" s="37" t="s">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="D133" s="38" t="s">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="E133" s="37" t="s">
-        <v>534</v>
+        <v>509</v>
       </c>
       <c r="F133" s="37" t="s">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="G133" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H133" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I133" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J133" s="37" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="K133" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L133" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M133" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="134" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9775,40 +9729,40 @@
         <v>7</v>
       </c>
       <c r="B134" s="28" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="C134" s="29" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="D134" s="30" t="s">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="E134" s="29" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="F134" s="29" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="G134" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H134" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I134" s="49" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J134" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K134" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L134" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M134" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="135" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9816,40 +9770,40 @@
         <v>8</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="C135" s="37" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="D135" s="38" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="E135" s="37" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="F135" s="37" t="s">
-        <v>545</v>
+        <v>520</v>
       </c>
       <c r="G135" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H135" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I135" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J135" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K135" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L135" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M135" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="136" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9857,40 +9811,40 @@
         <v>9</v>
       </c>
       <c r="B136" s="28" t="s">
-        <v>546</v>
+        <v>521</v>
       </c>
       <c r="C136" s="29" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E136" s="29" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="F136" s="29" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G136" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H136" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I136" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J136" s="29" t="s">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="K136" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L136" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M136" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="137" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9898,45 +9852,45 @@
         <v>10</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="C137" s="37" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="D137" s="38" t="s">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="E137" s="37" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
       <c r="F137" s="37" t="s">
-        <v>556</v>
+        <v>531</v>
       </c>
       <c r="G137" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H137" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I137" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J137" s="37" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K137" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L137" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M137" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="23" t="s">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="B139" s="23"/>
       <c r="C139" s="23"/>
@@ -9949,13 +9903,14 @@
       <c r="J139" s="23"/>
       <c r="K139" s="23"/>
       <c r="L139" s="23"/>
-      <c r="M139" s="24" t="s">
-        <v>55</v>
+      <c r="M139" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="25" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="B140" s="25"/>
       <c r="C140" s="25"/>
@@ -9972,43 +9927,43 @@
     </row>
     <row r="141" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B141" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C141" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E141" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G141" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H141" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I141" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J141" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K141" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L141" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M141" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10016,40 +9971,40 @@
         <v>1</v>
       </c>
       <c r="B142" s="28" t="s">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="C142" s="29" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="D142" s="30" t="s">
-        <v>561</v>
+        <v>536</v>
       </c>
       <c r="E142" s="29" t="s">
-        <v>562</v>
+        <v>537</v>
       </c>
       <c r="F142" s="29" t="s">
-        <v>563</v>
+        <v>538</v>
       </c>
       <c r="G142" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H142" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I142" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J142" s="29" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="K142" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L142" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M142" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="143" ht="126" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10057,40 +10012,40 @@
         <v>2</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>564</v>
+        <v>539</v>
       </c>
       <c r="C143" s="37" t="s">
-        <v>565</v>
+        <v>540</v>
       </c>
       <c r="D143" s="38" t="s">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="E143" s="37" t="s">
-        <v>567</v>
+        <v>542</v>
       </c>
       <c r="F143" s="37" t="s">
-        <v>568</v>
+        <v>543</v>
       </c>
       <c r="G143" s="35" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H143" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I143" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J143" s="37" t="s">
-        <v>569</v>
+        <v>544</v>
       </c>
       <c r="K143" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L143" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M143" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="144" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10098,40 +10053,40 @@
         <v>3</v>
       </c>
       <c r="B144" s="28" t="s">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="C144" s="29" t="s">
-        <v>571</v>
+        <v>546</v>
       </c>
       <c r="D144" s="30" t="s">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="E144" s="29" t="s">
-        <v>573</v>
+        <v>548</v>
       </c>
       <c r="F144" s="29" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="G144" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H144" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I144" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J144" s="29" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K144" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L144" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M144" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="145" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10139,40 +10094,40 @@
         <v>4</v>
       </c>
       <c r="B145" s="36" t="s">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="C145" s="37" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="D145" s="38" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="E145" s="37" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
       <c r="F145" s="37" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="G145" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H145" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I145" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J145" s="37" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="K145" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L145" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M145" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="146" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10180,40 +10135,40 @@
         <v>5</v>
       </c>
       <c r="B146" s="28" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="C146" s="29" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="D146" s="30" t="s">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="E146" s="29" t="s">
-        <v>584</v>
+        <v>559</v>
       </c>
       <c r="F146" s="29" t="s">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="G146" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H146" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I146" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J146" s="29" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K146" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L146" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M146" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10221,40 +10176,40 @@
         <v>6</v>
       </c>
       <c r="B147" s="36" t="s">
-        <v>586</v>
+        <v>561</v>
       </c>
       <c r="C147" s="37" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="D147" s="38" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="E147" s="37" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="F147" s="37" t="s">
-        <v>590</v>
+        <v>565</v>
       </c>
       <c r="G147" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H147" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I147" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J147" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K147" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L147" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M147" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="148" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10262,45 +10217,45 @@
         <v>7</v>
       </c>
       <c r="B148" s="28" t="s">
-        <v>591</v>
+        <v>566</v>
       </c>
       <c r="C148" s="29" t="s">
-        <v>592</v>
+        <v>567</v>
       </c>
       <c r="D148" s="30" t="s">
-        <v>593</v>
+        <v>568</v>
       </c>
       <c r="E148" s="29" t="s">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="F148" s="29" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="G148" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H148" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I148" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J148" s="29" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K148" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L148" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M148" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="150" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="B150" s="23"/>
       <c r="C150" s="23"/>
@@ -10313,13 +10268,14 @@
       <c r="J150" s="23"/>
       <c r="K150" s="23"/>
       <c r="L150" s="23"/>
-      <c r="M150" s="24" t="s">
-        <v>55</v>
+      <c r="M150" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="25" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B151" s="25"/>
       <c r="C151" s="25"/>
@@ -10336,43 +10292,43 @@
     </row>
     <row r="152" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B152" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C152" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E152" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G152" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H152" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I152" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J152" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K152" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L152" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M152" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10380,40 +10336,40 @@
         <v>1</v>
       </c>
       <c r="B153" s="28" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C153" s="29" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="D153" s="30" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="F153" s="29" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="G153" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H153" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I153" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J153" s="29" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="K153" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L153" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M153" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="154" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10421,40 +10377,40 @@
         <v>2</v>
       </c>
       <c r="B154" s="36" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="C154" s="37" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D154" s="38" t="s">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="E154" s="37" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="F154" s="37" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="G154" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H154" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I154" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J154" s="37" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K154" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L154" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M154" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="155" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10462,40 +10418,40 @@
         <v>3</v>
       </c>
       <c r="B155" s="28" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="C155" s="29" t="s">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="D155" s="30" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="F155" s="29" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="G155" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H155" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I155" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J155" s="29" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="K155" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L155" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M155" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="156" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10503,40 +10459,40 @@
         <v>4</v>
       </c>
       <c r="B156" s="36" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="C156" s="37" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="D156" s="38" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="E156" s="37" t="s">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="F156" s="37" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="G156" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H156" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I156" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J156" s="37" t="s">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="K156" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L156" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M156" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="157" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10544,40 +10500,40 @@
         <v>5</v>
       </c>
       <c r="B157" s="28" t="s">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="C157" s="29" t="s">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="D157" s="30" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="F157" s="29" t="s">
-        <v>623</v>
+        <v>598</v>
       </c>
       <c r="G157" s="27" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H157" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I157" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J157" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K157" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L157" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M157" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="158" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10585,45 +10541,45 @@
         <v>6</v>
       </c>
       <c r="B158" s="36" t="s">
-        <v>624</v>
+        <v>599</v>
       </c>
       <c r="C158" s="37" t="s">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="D158" s="38" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="E158" s="37" t="s">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="F158" s="37" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="G158" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H158" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I158" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J158" s="37" t="s">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="K158" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L158" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M158" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="160" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="23" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="B160" s="23"/>
       <c r="C160" s="23"/>
@@ -10636,13 +10592,14 @@
       <c r="J160" s="23"/>
       <c r="K160" s="23"/>
       <c r="L160" s="23"/>
-      <c r="M160" s="24" t="s">
-        <v>55</v>
+      <c r="M160" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="25" t="s">
-        <v>630</v>
+        <v>605</v>
       </c>
       <c r="B161" s="25"/>
       <c r="C161" s="25"/>
@@ -10659,43 +10616,43 @@
     </row>
     <row r="162" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B162" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C162" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D162" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E162" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F162" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G162" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H162" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I162" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J162" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K162" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L162" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M162" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10703,40 +10660,40 @@
         <v>1</v>
       </c>
       <c r="B163" s="28" t="s">
-        <v>631</v>
+        <v>606</v>
       </c>
       <c r="C163" s="29" t="s">
-        <v>632</v>
+        <v>607</v>
       </c>
       <c r="D163" s="30" t="s">
-        <v>633</v>
+        <v>608</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
       <c r="F163" s="29" t="s">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="G163" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H163" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I163" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J163" s="29" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K163" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L163" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M163" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10744,45 +10701,45 @@
         <v>2</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="C164" s="37" t="s">
-        <v>637</v>
+        <v>612</v>
       </c>
       <c r="D164" s="38" t="s">
-        <v>638</v>
+        <v>613</v>
       </c>
       <c r="E164" s="37" t="s">
-        <v>639</v>
+        <v>614</v>
       </c>
       <c r="F164" s="37" t="s">
-        <v>640</v>
+        <v>615</v>
       </c>
       <c r="G164" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H164" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I164" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J164" s="37" t="s">
-        <v>641</v>
+        <v>616</v>
       </c>
       <c r="K164" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L164" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M164" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="23" t="s">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="B166" s="23"/>
       <c r="C166" s="23"/>
@@ -10795,13 +10752,14 @@
       <c r="J166" s="23"/>
       <c r="K166" s="23"/>
       <c r="L166" s="23"/>
-      <c r="M166" s="24" t="s">
-        <v>55</v>
+      <c r="M166" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
-        <v>643</v>
+        <v>618</v>
       </c>
       <c r="B167" s="25"/>
       <c r="C167" s="25"/>
@@ -10818,43 +10776,43 @@
     </row>
     <row r="168" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B168" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C168" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D168" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E168" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F168" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G168" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H168" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I168" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J168" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K168" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L168" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M168" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10862,40 +10820,40 @@
         <v>1</v>
       </c>
       <c r="B169" s="28" t="s">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="C169" s="29" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>647</v>
+        <v>622</v>
       </c>
       <c r="F169" s="29" t="s">
-        <v>648</v>
+        <v>623</v>
       </c>
       <c r="G169" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H169" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I169" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J169" s="29" t="s">
-        <v>649</v>
+        <v>624</v>
       </c>
       <c r="K169" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L169" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M169" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10903,40 +10861,40 @@
         <v>2</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="C170" s="37" t="s">
-        <v>651</v>
+        <v>626</v>
       </c>
       <c r="D170" s="38" t="s">
-        <v>652</v>
+        <v>627</v>
       </c>
       <c r="E170" s="37" t="s">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="F170" s="37" t="s">
-        <v>654</v>
+        <v>629</v>
       </c>
       <c r="G170" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H170" s="48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I170" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J170" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K170" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L170" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M170" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="171" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10944,40 +10902,40 @@
         <v>3</v>
       </c>
       <c r="B171" s="28" t="s">
-        <v>655</v>
+        <v>630</v>
       </c>
       <c r="C171" s="29" t="s">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="D171" s="30" t="s">
-        <v>657</v>
+        <v>632</v>
       </c>
       <c r="E171" s="29" t="s">
-        <v>658</v>
+        <v>633</v>
       </c>
       <c r="F171" s="29" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="G171" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H171" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I171" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J171" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K171" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L171" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M171" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="172" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10985,40 +10943,40 @@
         <v>4</v>
       </c>
       <c r="B172" s="36" t="s">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="C172" s="37" t="s">
-        <v>661</v>
+        <v>636</v>
       </c>
       <c r="D172" s="38" t="s">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="E172" s="37" t="s">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="F172" s="37" t="s">
-        <v>664</v>
+        <v>639</v>
       </c>
       <c r="G172" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H172" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I172" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J172" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K172" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L172" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M172" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11026,45 +10984,45 @@
         <v>5</v>
       </c>
       <c r="B173" s="28" t="s">
-        <v>665</v>
+        <v>640</v>
       </c>
       <c r="C173" s="29" t="s">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="D173" s="30" t="s">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="E173" s="29" t="s">
-        <v>668</v>
+        <v>643</v>
       </c>
       <c r="F173" s="29" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="G173" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H173" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I173" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J173" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K173" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L173" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M173" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="175" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="23" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="B175" s="23"/>
       <c r="C175" s="23"/>
@@ -11077,13 +11035,14 @@
       <c r="J175" s="23"/>
       <c r="K175" s="23"/>
       <c r="L175" s="23"/>
-      <c r="M175" s="24" t="s">
-        <v>55</v>
+      <c r="M175" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
-        <v>671</v>
+        <v>646</v>
       </c>
       <c r="B176" s="25"/>
       <c r="C176" s="25"/>
@@ -11100,43 +11059,43 @@
     </row>
     <row r="177" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B177" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C177" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D177" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E177" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F177" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G177" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H177" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I177" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J177" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K177" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L177" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M177" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="178" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11144,40 +11103,40 @@
         <v>1</v>
       </c>
       <c r="B178" s="28" t="s">
-        <v>672</v>
+        <v>647</v>
       </c>
       <c r="C178" s="29" t="s">
-        <v>673</v>
+        <v>648</v>
       </c>
       <c r="D178" s="30" t="s">
-        <v>674</v>
+        <v>649</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="F178" s="29" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="G178" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H178" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I178" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J178" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K178" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L178" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M178" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="179" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11185,40 +11144,40 @@
         <v>2</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="C179" s="37" t="s">
-        <v>678</v>
+        <v>653</v>
       </c>
       <c r="D179" s="38" t="s">
-        <v>679</v>
+        <v>654</v>
       </c>
       <c r="E179" s="37" t="s">
-        <v>680</v>
+        <v>655</v>
       </c>
       <c r="F179" s="37" t="s">
-        <v>681</v>
+        <v>656</v>
       </c>
       <c r="G179" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H179" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I179" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J179" s="37" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="K179" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L179" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M179" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="180" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11226,40 +11185,40 @@
         <v>3</v>
       </c>
       <c r="B180" s="28" t="s">
-        <v>682</v>
+        <v>657</v>
       </c>
       <c r="C180" s="29" t="s">
-        <v>683</v>
+        <v>658</v>
       </c>
       <c r="D180" s="30" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>685</v>
+        <v>660</v>
       </c>
       <c r="F180" s="29" t="s">
-        <v>686</v>
+        <v>661</v>
       </c>
       <c r="G180" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H180" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I180" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J180" s="29" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="K180" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L180" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M180" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="181" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11267,45 +11226,45 @@
         <v>4</v>
       </c>
       <c r="B181" s="36" t="s">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="C181" s="37" t="s">
-        <v>688</v>
+        <v>663</v>
       </c>
       <c r="D181" s="38" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E181" s="37" t="s">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="F181" s="37" t="s">
-        <v>690</v>
+        <v>665</v>
       </c>
       <c r="G181" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H181" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I181" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J181" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K181" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L181" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M181" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="183" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="23" t="s">
-        <v>691</v>
+        <v>666</v>
       </c>
       <c r="B183" s="23"/>
       <c r="C183" s="23"/>
@@ -11318,13 +11277,14 @@
       <c r="J183" s="23"/>
       <c r="K183" s="23"/>
       <c r="L183" s="23"/>
-      <c r="M183" s="24" t="s">
-        <v>55</v>
+      <c r="M183" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
-        <v>692</v>
+        <v>667</v>
       </c>
       <c r="B184" s="25"/>
       <c r="C184" s="25"/>
@@ -11341,43 +11301,43 @@
     </row>
     <row r="185" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B185" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C185" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D185" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E185" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F185" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G185" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H185" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I185" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J185" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K185" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L185" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M185" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" ht="66" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11385,40 +11345,40 @@
         <v>1</v>
       </c>
       <c r="B186" s="28" t="s">
-        <v>693</v>
+        <v>668</v>
       </c>
       <c r="C186" s="29" t="s">
-        <v>694</v>
+        <v>669</v>
       </c>
       <c r="D186" s="30" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="F186" s="29" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="G186" s="27" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H186" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I186" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J186" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K186" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L186" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M186" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="187" ht="51" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11426,45 +11386,45 @@
         <v>2</v>
       </c>
       <c r="B187" s="36" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="C187" s="37" t="s">
-        <v>699</v>
+        <v>674</v>
       </c>
       <c r="D187" s="38" t="s">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="E187" s="37" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="F187" s="37" t="s">
-        <v>702</v>
+        <v>677</v>
       </c>
       <c r="G187" s="35" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="H187" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I187" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J187" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K187" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L187" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M187" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="189" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="23" t="s">
-        <v>703</v>
+        <v>678</v>
       </c>
       <c r="B189" s="23"/>
       <c r="C189" s="23"/>
@@ -11477,13 +11437,14 @@
       <c r="J189" s="23"/>
       <c r="K189" s="23"/>
       <c r="L189" s="23"/>
-      <c r="M189" s="24" t="s">
-        <v>55</v>
+      <c r="M189" s="24" t="str">
+        <f>HYPERLINK("#'Test Cases'!A5","↑ Summary")</f>
+        <v>↑ Summary</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
-        <v>704</v>
+        <v>679</v>
       </c>
       <c r="B190" s="25"/>
       <c r="C190" s="25"/>
@@ -11500,43 +11461,43 @@
     </row>
     <row r="191" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="26" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B191" s="26" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C191" s="26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D191" s="26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E191" s="26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F191" s="26" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G191" s="26" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H191" s="26" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="I191" s="26" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J191" s="26" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K191" s="26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L191" s="26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M191" s="26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11544,40 +11505,40 @@
         <v>1</v>
       </c>
       <c r="B192" s="28" t="s">
-        <v>705</v>
+        <v>680</v>
       </c>
       <c r="C192" s="29" t="s">
-        <v>706</v>
+        <v>681</v>
       </c>
       <c r="D192" s="30" t="s">
-        <v>707</v>
+        <v>682</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>708</v>
+        <v>683</v>
       </c>
       <c r="F192" s="29" t="s">
-        <v>709</v>
+        <v>684</v>
       </c>
       <c r="G192" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H192" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I192" s="44" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J192" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K192" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L192" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M192" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="193" ht="111" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11585,40 +11546,40 @@
         <v>2</v>
       </c>
       <c r="B193" s="36" t="s">
-        <v>710</v>
+        <v>685</v>
       </c>
       <c r="C193" s="37" t="s">
-        <v>711</v>
+        <v>686</v>
       </c>
       <c r="D193" s="38" t="s">
-        <v>712</v>
+        <v>687</v>
       </c>
       <c r="E193" s="37" t="s">
-        <v>713</v>
+        <v>688</v>
       </c>
       <c r="F193" s="37" t="s">
-        <v>714</v>
+        <v>689</v>
       </c>
       <c r="G193" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H193" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I193" s="42" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J193" s="37" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="K193" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L193" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M193" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="194" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11626,40 +11587,40 @@
         <v>3</v>
       </c>
       <c r="B194" s="28" t="s">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="C194" s="29" t="s">
-        <v>716</v>
+        <v>691</v>
       </c>
       <c r="D194" s="30" t="s">
-        <v>717</v>
+        <v>692</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>718</v>
+        <v>693</v>
       </c>
       <c r="F194" s="29" t="s">
-        <v>719</v>
+        <v>694</v>
       </c>
       <c r="G194" s="27" t="s">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="H194" s="31" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I194" s="49" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J194" s="29" t="s">
-        <v>721</v>
+        <v>696</v>
       </c>
       <c r="K194" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L194" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M194" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="195" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11667,40 +11628,40 @@
         <v>4</v>
       </c>
       <c r="B195" s="36" t="s">
-        <v>722</v>
+        <v>697</v>
       </c>
       <c r="C195" s="37" t="s">
-        <v>723</v>
+        <v>698</v>
       </c>
       <c r="D195" s="38" t="s">
-        <v>724</v>
+        <v>699</v>
       </c>
       <c r="E195" s="37" t="s">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="F195" s="37" t="s">
-        <v>726</v>
+        <v>701</v>
       </c>
       <c r="G195" s="35" t="s">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="H195" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I195" s="47" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="J195" s="37" t="s">
-        <v>721</v>
+        <v>696</v>
       </c>
       <c r="K195" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L195" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M195" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="196" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11708,40 +11669,40 @@
         <v>5</v>
       </c>
       <c r="B196" s="28" t="s">
-        <v>727</v>
+        <v>702</v>
       </c>
       <c r="C196" s="29" t="s">
-        <v>728</v>
+        <v>703</v>
       </c>
       <c r="D196" s="30" t="s">
-        <v>729</v>
+        <v>704</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="F196" s="29" t="s">
-        <v>731</v>
+        <v>706</v>
       </c>
       <c r="G196" s="27" t="s">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="H196" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I196" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J196" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K196" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L196" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M196" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="197" ht="111" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11749,40 +11710,40 @@
         <v>6</v>
       </c>
       <c r="B197" s="36" t="s">
-        <v>732</v>
+        <v>707</v>
       </c>
       <c r="C197" s="37" t="s">
-        <v>733</v>
+        <v>708</v>
       </c>
       <c r="D197" s="38" t="s">
-        <v>734</v>
+        <v>709</v>
       </c>
       <c r="E197" s="37" t="s">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="F197" s="37" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="G197" s="35" t="s">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="H197" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I197" s="40" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J197" s="37" t="s">
-        <v>737</v>
+        <v>712</v>
       </c>
       <c r="K197" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L197" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M197" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="198" ht="96" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11790,40 +11751,40 @@
         <v>7</v>
       </c>
       <c r="B198" s="28" t="s">
-        <v>738</v>
+        <v>713</v>
       </c>
       <c r="C198" s="29" t="s">
-        <v>739</v>
+        <v>714</v>
       </c>
       <c r="D198" s="30" t="s">
-        <v>740</v>
+        <v>715</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="F198" s="29" t="s">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="G198" s="27" t="s">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="H198" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I198" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J198" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K198" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L198" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M198" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="199" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11831,40 +11792,40 @@
         <v>8</v>
       </c>
       <c r="B199" s="36" t="s">
-        <v>743</v>
+        <v>718</v>
       </c>
       <c r="C199" s="37" t="s">
-        <v>744</v>
+        <v>719</v>
       </c>
       <c r="D199" s="38" t="s">
-        <v>745</v>
+        <v>720</v>
       </c>
       <c r="E199" s="37" t="s">
-        <v>746</v>
+        <v>721</v>
       </c>
       <c r="F199" s="37" t="s">
-        <v>747</v>
+        <v>722</v>
       </c>
       <c r="G199" s="35" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H199" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I199" s="45" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J199" s="37" t="s">
-        <v>748</v>
+        <v>723</v>
       </c>
       <c r="K199" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L199" s="41" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M199" s="37" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="200" ht="81" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11872,40 +11833,40 @@
         <v>9</v>
       </c>
       <c r="B200" s="28" t="s">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="C200" s="29" t="s">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="D200" s="30" t="s">
-        <v>751</v>
+        <v>726</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>752</v>
+        <v>727</v>
       </c>
       <c r="F200" s="29" t="s">
-        <v>753</v>
+        <v>728</v>
       </c>
       <c r="G200" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H200" s="43" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I200" s="32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J200" s="29" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K200" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L200" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M200" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -11982,44 +11943,6 @@
     <mergeCell ref="A189:L189"/>
     <mergeCell ref="A190:M190"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" location="#'Test Cases'!A21"/>
-    <hyperlink ref="K7" r:id="rId2" location="#'Test Cases'!A21"/>
-    <hyperlink ref="B8" r:id="rId3" location="#'Test Cases'!A27"/>
-    <hyperlink ref="K8" r:id="rId4" location="#'Test Cases'!A27"/>
-    <hyperlink ref="B9" r:id="rId5" location="#'Test Cases'!A86"/>
-    <hyperlink ref="K9" r:id="rId6" location="#'Test Cases'!A86"/>
-    <hyperlink ref="B10" r:id="rId7" location="#'Test Cases'!A105"/>
-    <hyperlink ref="K10" r:id="rId8" location="#'Test Cases'!A105"/>
-    <hyperlink ref="B11" r:id="rId9" location="#'Test Cases'!A125"/>
-    <hyperlink ref="K11" r:id="rId10" location="#'Test Cases'!A125"/>
-    <hyperlink ref="B12" r:id="rId11" location="#'Test Cases'!A139"/>
-    <hyperlink ref="K12" r:id="rId12" location="#'Test Cases'!A139"/>
-    <hyperlink ref="B13" r:id="rId13" location="#'Test Cases'!A150"/>
-    <hyperlink ref="K13" r:id="rId14" location="#'Test Cases'!A150"/>
-    <hyperlink ref="B14" r:id="rId15" location="#'Test Cases'!A160"/>
-    <hyperlink ref="K14" r:id="rId16" location="#'Test Cases'!A160"/>
-    <hyperlink ref="B15" r:id="rId17" location="#'Test Cases'!A166"/>
-    <hyperlink ref="K15" r:id="rId18" location="#'Test Cases'!A166"/>
-    <hyperlink ref="B16" r:id="rId19" location="#'Test Cases'!A175"/>
-    <hyperlink ref="K16" r:id="rId20" location="#'Test Cases'!A175"/>
-    <hyperlink ref="B17" r:id="rId21" location="#'Test Cases'!A183"/>
-    <hyperlink ref="K17" r:id="rId22" location="#'Test Cases'!A183"/>
-    <hyperlink ref="B18" r:id="rId23" location="#'Test Cases'!A189"/>
-    <hyperlink ref="K18" r:id="rId24" location="#'Test Cases'!A189"/>
-    <hyperlink ref="M21" r:id="rId25" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M27" r:id="rId26" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M86" r:id="rId27" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M105" r:id="rId28" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M125" r:id="rId29" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M139" r:id="rId30" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M150" r:id="rId31" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M160" r:id="rId32" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M166" r:id="rId33" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M175" r:id="rId34" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M183" r:id="rId35" location="#'Test Cases'!A5"/>
-    <hyperlink ref="M189" r:id="rId36" location="#'Test Cases'!A5"/>
-  </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-09-30 08:37 UTC  ·  environment staging  ·  projects=api  ·  took 5s</t>
+    <t>Last run: 2026-09-30 09:15 UTC  ·  environment staging  ·  projects=api  ·  took 6.4s</t>
   </si>
   <si>
     <t>Total test cases: 55</t>
@@ -1067,10 +1067,10 @@
     <t>Broken emails would make password resets and notifications fail without anyone noticing.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller (permission is checked first, BQ-14) — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=b12648a9-7430-47af-ab24-7b01805de031, 93ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller (permission is checked first, BQ-14) — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=b12648a9-7430-47af-ab24-7b01805de031, 93ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller (permission is checked first, BQ-14) — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=7183c41d-3151-4ecb-97f2-7587d2a0f88d, 97ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller (permission is checked first, BQ-14) — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=7183c41d-3151-4ecb-97f2-7587d2a0f88d, 97ms)</t>
   </si>
   <si>
     <t>AISLE-WR-010</t>
@@ -1115,10 +1115,10 @@
     <t>Aisle compares and shows emails. If they are not cleaned up the same way every time, logins and look-ups can fail.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=dd4ee452-ac42-4bde-ad25-162e0c485df5, 113ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=dd4ee452-ac42-4bde-ad25-162e0c485df5, 113ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=6547f306-23e9-43a8-8c7f-8407c17539e7, 202ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=6547f306-23e9-43a8-8c7f-8407c17539e7, 202ms)</t>
   </si>
   <si>
     <t>POC-001</t>
@@ -1414,10 +1414,10 @@
     <t>Screens often ask for several fields at once. A field that is missing must not hide the ones that exist.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test/read -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=53a68365-563a-45b3-82af-57ed4f86fff9, 103ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test/read -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=53a68365-563a-45b3-82af-57ed4f86fff9, 103ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test/read -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=66197bd5-b9dd-4206-a625-de189b65a4af, 112ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test/read -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=66197bd5-b9dd-4206-a625-de189b65a4af, 112ms)</t>
   </si>
   <si>
     <t>AISLE-RD-003</t>
@@ -1662,10 +1662,10 @@
     <t>Aisle looks users up by email. Search must ignore case and spacing, and must not hand out emails nobody asked for.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=71de9a6e-01f5-4107-9c5c-9b2364e990a7, 88ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=71de9a6e-01f5-4107-9c5c-9b2364e990a7, 88ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=87812166-f343-46de-babd-72b87a1f243c, 167ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=87812166-f343-46de-babd-72b87a1f243c, 167ms)</t>
   </si>
   <si>
     <t>AISLE-SR-002</t>
@@ -1706,10 +1706,10 @@
     <t>Callers that are allowed to see values must get the clean stored form.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=0b8d3146-c7f4-4ad3-8be3-2bee2a30f0c4, 90ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=0b8d3146-c7f4-4ad3-8be3-2bee2a30f0c4, 90ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=7592038d-5049-49bf-8d96-ac7baf0522b3, 110ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=7592038d-5049-49bf-8d96-ac7baf0522b3, 110ms)</t>
   </si>
   <si>
     <t>AISLE-SR-003</t>
@@ -1750,10 +1750,10 @@
     <t>The limit keeps results small and safe. The caller must be told that more matches exist.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=4d618888-1803-44aa-8fcb-2656fb3a09f0, 89ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=4d618888-1803-44aa-8fcb-2656fb3a09f0, 89ms)</t>
+    <t>BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ac154701-b08f-4b50-8b9b-95e725727f93, 107ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL access not granted to the Aisle caller — observed POST /api/v1/pii-test -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ac154701-b08f-4b50-8b9b-95e725727f93, 107ms)</t>
   </si>
   <si>
     <t>AISLE-SR-004</t>
@@ -1832,10 +1832,10 @@
     <t>The app must handle “no match” without errors and without other people’s data.</t>
   </si>
   <si>
-    <t>BQ-01: EMAIL search access not granted to the Aisle caller — observed POST /api/v1/pii-test/EMAIL/search -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ffab37e6-2d86-4ef6-8d38-e80039f845ce, 83ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-01: EMAIL search access not granted to the Aisle caller — observed POST /api/v1/pii-test/EMAIL/search -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ffab37e6-2d86-4ef6-8d38-e80039f845ce, 83ms)</t>
+    <t>BQ-01: EMAIL search access not granted to the Aisle caller — observed POST /api/v1/pii-test/EMAIL/search -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=353212a6-e192-4c1f-9e44-fc9228c38416, 107ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-01: EMAIL search access not granted to the Aisle caller — observed POST /api/v1/pii-test/EMAIL/search -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=353212a6-e192-4c1f-9e44-fc9228c38416, 107ms)</t>
   </si>
   <si>
     <t>5.  Bulk read PII     POST /api/v1/pii-test/batch/read        6 test cases  ·  ✔ 6  ·  ✘ 0  ·  — 0</t>
@@ -2319,10 +2319,10 @@
     <t>Notes are encrypted with this key. It must be the right strength, must never be kept in caches and must never end up in our logs.</t>
   </si>
   <si>
-    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=bba93383-71ac-46e7-b306-e1787a25f020, 106ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=bba93383-71ac-46e7-b306-e1787a25f020, 106ms)</t>
+    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=44182b98-710f-4731-aff5-dd3406ba67fa, 149ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=44182b98-710f-4731-aff5-dd3406ba67fa, 149ms)</t>
   </si>
   <si>
     <t>10.  Read encryption key     POST /api/v1/pii-test/free-text/keys/read        1 test cases  ·  ✔ 0  ·  ✘ 0  ·  ⏸ 1 blocked  ·  — 0</t>
@@ -2372,10 +2372,10 @@
     <t>Encrypted notes can only be opened again with exactly the same key.</t>
   </si>
   <si>
-    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=28f992a7-efb5-4e42-9db9-71525b7c4321, 94ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=28f992a7-efb5-4e42-9db9-71525b7c4321, 94ms)</t>
+    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ac0ebd6e-ec7c-4f7a-bb62-bd786263eb4a, 119ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=ac0ebd6e-ec7c-4f7a-bb62-bd786263eb4a, 119ms)</t>
   </si>
   <si>
     <t>11.  Revoke encryption key     POST /api/v1/pii-test/free-text/keys/revoke        1 test cases  ·  ✔ 0  ·  ✘ 0  ·  ⏸ 1 blocked  ·  — 0</t>
@@ -2427,10 +2427,10 @@
     <t>Revoking must really switch a key off, for example after it leaked.</t>
   </si>
   <si>
-    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=161499ba-3158-4a75-bd74-1d9caf83858b, 92ms)</t>
-  </si>
-  <si>
-    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=161499ba-3158-4a75-bd74-1d9caf83858b, 92ms)</t>
+    <t>BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=c46ba4c8-8f56-4bb6-a6b7-b0b84ae3da13, 106ms)</t>
+  </si>
+  <si>
+    <t>BLOCKED — BQ-02: Free-text key access not granted to the Aisle caller — observed POST /api/v1/pii-test/free-text/keys -&gt; HTTP 403 code=AUTHORIZATION_DENIED (requestId=c46ba4c8-8f56-4bb6-a6b7-b0b84ae3da13, 106ms)</t>
   </si>
   <si>
     <t>12.  Across endpoints     several endpoints        4 test cases  ·  ✔ 4  ·  ✘ 0  ·  — 0</t>
